--- a/ValueSet-legemiddel-koder.xlsx
+++ b/ValueSet-legemiddel-koder.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T09:35:49+00:00</t>
+    <t>2026-03-10T12:49:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-legemiddel-koder.xlsx
+++ b/ValueSet-legemiddel-koder.xlsx
@@ -34,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.7</t>
+    <t>1.0.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T12:49:22+00:00</t>
+    <t>2026-03-10T15:33:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-legemiddel-koder.xlsx
+++ b/ValueSet-legemiddel-koder.xlsx
@@ -12,12 +12,15 @@
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
     <sheet name="Include #3" r:id="rId7" sheetId="5"/>
     <sheet name="Include #4" r:id="rId8" sheetId="6"/>
+    <sheet name="Include #5" r:id="rId9" sheetId="7"/>
+    <sheet name="Include #6" r:id="rId10" sheetId="8"/>
+    <sheet name="Include #7" r:id="rId11" sheetId="9"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="40">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T15:33:20+00:00</t>
+    <t>2026-03-18T15:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,7 +91,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet som inneholder koder fra SNOMED CT og FEST</t>
+    <t>ValueSet som inneholder koder fra SNOMED CT, FEST, LMR-nummer, varenummer og lokal legemiddelkatalog</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -128,6 +131,15 @@
   </si>
   <si>
     <t>http://dmp.no/fhir/NamingSystem/festLegemiddelDose</t>
+  </si>
+  <si>
+    <t>http://dmp.no/fhir/NamingSystem/lmrLopenummer</t>
+  </si>
+  <si>
+    <t>http://dmp.no/fhir/NamingSystem/fest-varenummer</t>
+  </si>
+  <si>
+    <t>http://fh.no/fhir/NamingSystem/lokaltVirkemiddel</t>
   </si>
 </sst>
 </file>
@@ -593,4 +605,124 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ValueSet-legemiddel-koder.xlsx
+++ b/ValueSet-legemiddel-koder.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.8</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -55,7 +55,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T15:02:12+00:00</t>
+    <t>2026-04-21T11:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -139,7 +139,7 @@
     <t>http://dmp.no/fhir/NamingSystem/fest-varenummer</t>
   </si>
   <si>
-    <t>http://fh.no/fhir/NamingSystem/lokaltVirkemiddel</t>
+    <t>http://fhi.no/fhir/NamingSystem/lokaltLegemiddel</t>
   </si>
 </sst>
 </file>

--- a/ValueSet-legemiddel-koder.xlsx
+++ b/ValueSet-legemiddel-koder.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T07:26:56+00:00</t>
+    <t>2026-05-11T08:19:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-legemiddel-koder.xlsx
+++ b/ValueSet-legemiddel-koder.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T08:19:23+00:00</t>
+    <t>2026-05-31T19:08:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-legemiddel-koder.xlsx
+++ b/ValueSet-legemiddel-koder.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>1.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-31T19:08:08+00:00</t>
+    <t>2026-06-12T10:49:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-legemiddel-koder.xlsx
+++ b/ValueSet-legemiddel-koder.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.1.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T10:49:58+00:00</t>
+    <t>2026-08-24T07:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
